--- a/important_mails_2026-05-18.xlsx
+++ b/important_mails_2026-05-18.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H188"/>
+  <dimension ref="A1:H185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -485,37 +485,89 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 18 May 2026 13:46:45 +0000</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Your payment is on the way</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Congratulations! Your payment is on the way and will arrive soon.
+ Disbursement Attempted
+Congratulations Weihai EU! Your payment is on the way and will arrive within three to five days.
+On 05/18/26 13:46 CEST, we initiated a transfer to your payment method (bank account ending in 229) in the amount of €
+ 256.29.
+ If the amount is less than expected, here are a few questions to consider:
+ Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims, or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
+ Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees, and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
+To learn more about Payment Reports in Seller Central, please visit our official course.
+We wish you continued success!
+Thank you for selling in the Amazon store,
+Amazon Services
+Help us improve your payment experience on Ama</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 07:24:17 +0000</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-vendor@amazon.com.mx" &lt;cscompliance-docreview-vendor@amazon.com.mx&gt;</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 771770 - CSC
  - DOC REVIEW</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -531,40 +583,40 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 07:03:38 +0000</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.it" &lt;cscompliance-docreview-seller@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
  APJ6JRA9NG5V4 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -578,40 +630,40 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 07:02:28 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.it" &lt;cscompliance-docreview-seller@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0G6XCTGJC, MARKETPLACE:
  APJ6JRA9NG5V4 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -625,39 +677,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 14:33:15 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $105.47 in an attempt to settle your Amazon seller account balance.
@@ -673,39 +725,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 02:39:33 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (ZazNpo+O9J)</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -731,39 +783,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Tue, 12 May 2026 02:56:06 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -779,39 +831,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 08:49:45 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -831,39 +883,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 08:47:51 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -883,39 +935,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Fri, 15 May 2026 15:36:52 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -935,39 +987,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 14:51:22 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -983,39 +1035,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 14:50:04 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1032,39 +1084,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 14:49:55 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1084,39 +1136,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Wed, 13 May 2026 14:53:51 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Download your China tax report for October - December 2025</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>96
  You can now download your quarterly tax report which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -1133,40 +1185,40 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 14:07:57 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>"toys-safety-mv@amazon.com" &lt;toys-safety-mv@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ,
  MARKETPLACE: 1 - PS - APPEAL</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Hello,
 We have reviewed your appeal request. We are rejecting your appeal because the detail page has an image of a child playing with the product. We request you take the following action:
@@ -1179,39 +1231,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 03:03:13 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -1231,39 +1283,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Fri, 15 May 2026 07:42:16 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-de@amazon.com" &lt;fba-3p-buyability-improvement-de@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>主题：需要采取的行动：网站禁止的 ASIN</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家，
 我们与您联系是为了让您知道，由于您的某些 ASIN 被禁止显示，您可能会错失销售机会.
@@ -1288,39 +1340,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 10:44:21 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-it@amazon.com" &lt;fba-3p-buyability-improvement-it@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>主题：需要采取的行动：网站禁止的 ASIN</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家，
 我们与您联系是为了让您知道，由于您的某些 ASIN 被禁止显示，您可能会错失销售机会.
@@ -1345,58 +1397,10 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 11 May 2026 09:19:51 +0000</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
- DOC REVIEW</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>Do not reply back to this e-mail!
-Hello,
-Thank you for submitting a document to the Chemical Safety Compliance Team.
-Upon review, we determined that the Safety Data Sheet ( SDS ) you uploaded for your ASIN is invalid due to it being incomplete, inaccurate, or otherwise conflicting, and thus, cannot be used for classification. Even though you've provided a written statement asserting that this SDS is the correct one, unfortunately, it doesn't validate its applicability for your product due to the following issues with the SDS:
-→ The name/title of the product on the SDS is " See item 3 for details " while the listing name/title of the product is "12 color acrylic paint ".
-→ The SDS must be composed in accordance with a valid regulation/legislation for Chemical Safety Compliance( for which your product is listed and stored ).
-The SDS does not include the legislation/regulation in accordance with the document was created
-Legislation/regulation should be also mentioned in section 2 “Hazard Identification”.
-→ The SDS must be composed in accordance with a valid regulation/legislation for Chemical Safety Compliance( for which your product is listed and stored ).
-The SDS does not include th</t>
-        </is>
-      </c>
-    </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>产品链接/合规类</t>
+          <t>法务/侵权类</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1411,115 +1415,21 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 09:19:28 +0000</t>
+          <t>Sun, 17 May 2026 08:48:46 +0000</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>"cscompliance-docreview-vendor@amazon.com.mx" &lt;cscompliance-docreview-vendor@amazon.com.mx&gt;</t>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 771770 - CSC
- - DOC REVIEW</t>
+          <t>Pagamento elaborato con successo</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>Do not reply back to this e-mail!
-Hello,
-Thank you for submitting a document to the Chemical Safety Compliance Team.
-Upon review, we determined that the Safety Data Sheet ( SDS ) you uploaded for your ASIN is invalid due to it being incomplete, inaccurate, or otherwise conflicting, and thus, cannot be used for classification. Even though you've provided a written statement asserting that this SDS is the correct one, unfortunately, it doesn't validate its applicability for your product due to the following issues with the SDS:
-→ The SDS must be composed in accordance with a valid regulation/legislation for Chemical Safety Compliance( for which your product is listed and stored ).
-The SDS does not include the legislation/regulation in accordance with the document was created
-Legislation/regulation should be also mentioned in section 2 “Hazard Identification”.
-For guidance on Safety Data Sheet requirements, please refer to https://sellercentral.amazon.com/help/hub/reference/G5G6BBSA6FZQP9CP
-Once you have corrected the problems listed above, please re-upload a valid document in Account Health Dashboard under "Regulatory Compliance" section. For any questions/appeals regarding these pro</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 11 May 2026 09:15:37 +0000</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0G6XCTGJC, MARKETPLACE:
- A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>Do not reply back to this e-mail!
-Hello,
-Thank you for submitting a document to the Chemical Safety Compliance Team.
-Upon review, we determined that the Safety Data Sheet ( SDS ) you uploaded for your ASIN is invalid due to it being incomplete, inaccurate, or otherwise conflicting, and thus, cannot be used for classification. Even though you've provided a written statement asserting that this SDS is the correct one, unfortunately, it doesn't validate its applicability for your product due to the following issues with the SDS:
-→ The SDS must be composed in accordance with a valid regulation/legislation for Chemical Safety Compliance( for which your product is listed and stored ).
-The SDS does not include the legislation/regulation in accordance with the document was created
-Legislation/regulation should be also mentioned in section 2 “Hazard Identification”.
-For guidance on Safety Data Sheet requirements, please refer to https://sellercentral.amazon.com/help/hub/reference/G5G6BBSA6FZQP9CP
-Once you have corrected the problems listed above, please re-upload a valid document in Account Health Dashboard under "Regulatory Compliance" section. For any questions/appeals regarding these pro</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 17 May 2026 08:48:46 +0000</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Pagamento elaborato con successo</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -1534,40 +1444,40 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 05:21:00 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>"Amazon.co.uk" &lt;store-news@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Swimming Training Belt, 2.5-7.5M Adjustable Swimming Resistance
  Bands is still in your basket</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.co.uk/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -1583,39 +1493,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Sat, 16 May 2026 17:10:29 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -1631,39 +1541,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Fri, 15 May 2026 15:52:25 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;store-news@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>EchoPlan Magnetic Blocks is still in your cart</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Still thinking about it? https://www.amazon.com/gp/cart/view.html?ref_=cor
 EchoPlan 200PCS Magnetic Blocks, Magnetic Building Blocks, Magnet Blocks Cubes, STEM Educational Stacking Magnet Toy for Kids Ages 3 4 5 6 7 8 9 10 11, Birthday Gifts for Boys and Girls, 1&amp;quot; Large Size
@@ -1684,39 +1594,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 14:07:42 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -1731,39 +1641,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 03:00:00 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -1793,39 +1703,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Wed, 13 May 2026 16:40:18 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -1853,39 +1763,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Wed, 13 May 2026 14:51:48 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Zespół Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Pobierz raport podatkowy dla Chin za okres od października do grudnia 2025 r.</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Możesz teraz pobrać kwartalny raport podatkowy, który zawiera dane, takie jak informacje identyfikacyjne, liczba transakcji, przychody oraz prowizje i opłaty za usługi.
@@ -1901,39 +1811,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Tue, 12 May 2026 10:10:51 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>EPR Pay on Behalf charges for 2024 Amazon.co.uk sales</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -1952,93 +1862,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 11 May 2026 12:21:34 +0000</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>Dein Einkaufswagen wartet</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
-Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
- -7 % 21,81 € UVP: 23,49 €
-https://www.amazon.de/gp/product/B0DRCB74YN/?ref_=
-Einkaufswagen anzeigen
-https://www.amazon.de/gp/cart/view.html?ref_=cor
-Schaue dir weitere Optionen an
-75x120 cm Feuerfeste Unterlage, Hitzeschutzmatte, Antihaft-Material Bodenschutzmatte, Grill Matten, Bodenmatte Feuerstellenmatte Outdoor BBQ Matte für Gasgrill Holzkohlegrill
- 16,80 €
-https://www.amazon.de/gp/product/B0DBLM41YS/?ref_=ci_mcx_mr_2p_0_lm
-Alckijy Feuerfeste Unterlage | 100 * 150cm Faltbare Hitzeschutzmatte | Bodenschutzmatte | Grillmatten | Bodenmatte | Grillteppich | Funkenschutzplatte | für BBQ Grills Kaminöfen Boden Rasen usw
- -4 % 20,15 € UVP: 20,97 €
-https://www.amazon.de/gp/product/B0CSGBZG8W/?ref_=ci_mcx_mr_2p_1_lm
-FLASLD Feuerfeste Matte Hitzebeständig Grillmatte unter Blackgrillstone, 40 x 60 cm schützt Ihren Vorbereitungstisch und Grilltisch im Freien – hitzebeständige Grilltischmatte schwarz
- 8,39 €
-https://www.amazon.de/gp/product/B0C9ZR7PGP/?ref_=ci_mcx_mr_2p_2_lm
-We</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Sat, 16 May 2026 04:51:55 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-28</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -2062,39 +1918,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Sat, 16 May 2026 03:58:34 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-28</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -2115,39 +1971,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Sat, 16 May 2026 03:50:26 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -2170,80 +2026,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 11 May 2026 11:38:29 +0000</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>You have until July 11 to verify FBA dimensions for fee calculation</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">As previously communicated, we've updated the way we collect Fulfilment by Amazon (FBA) item package dimensions for products listed in our UK, Germany, France, Italy and Spain stores.
- 96
- As previously communicated, we've updated the way we collect Fulfilment by Amazon (FBA) item package dimensions for products listed in our UK, Germany, France, Italy and Spain stores.
-                                                     ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ </t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Sun, 10 May 2026 16:45:41 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (Xq4e6nl040)</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2268,39 +2083,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 05:42:00 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (zl4CmeMn1C)</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2320,39 +2135,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 18:10:42 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (toabAY9R4I)</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2372,39 +2187,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 11:59:35 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (cp3IU6ppnV)</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2424,39 +2239,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Wed, 6 May 2026 16:07:01 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2477,39 +2292,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 13:03:07 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (2604121A02)</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2529,39 +2344,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Mon, 4 May 2026 16:59:42 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (AOOD6vlnxr)</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2581,39 +2396,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 14:32:02 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $69.79 in an attempt to settle your Amazon seller account balance.
@@ -2629,39 +2444,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 07:28:26 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (5NT+O11io4)</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2681,39 +2496,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:54:23 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $44.85 in an attempt to settle your Amazon seller account balance.
@@ -2729,39 +2544,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:03:42 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2778,39 +2593,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:03:28 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2830,39 +2645,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:01:21 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2882,39 +2697,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 03:44:19 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2931,39 +2746,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 15:00:39 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 87.72 in an attempt to settle your account balance.
@@ -2978,39 +2793,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 14:45:41 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -3026,39 +2841,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 15:23:38 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>欧洲亚马逊 Payments &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>跨账户负余额调整</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3078,39 +2893,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 23:31:40 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3130,39 +2945,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:27:01 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3179,39 +2994,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:26:48 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3231,39 +3046,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 17:03:06 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3283,39 +3098,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Apr 2026 14:08:56 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3332,39 +3147,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Apr 2026 14:08:50 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3384,39 +3199,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Apr 2026 05:12:21 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;seller-notification@amazon.ie&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Outstanding balance on your Amazon account</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>Hello,
  You have an outstanding balance on your account in the amount of 7,79 EUR. We will debit this amount from the credit card (Visa) that you registered as the charge method for your account.
@@ -3430,39 +3245,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 15:01:26 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3482,39 +3297,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 14:27:43 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3531,39 +3346,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:45:45 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -3579,39 +3394,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:44:32 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3631,41 +3446,183 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 11 May 2026 09:19:51 +0000</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
+ DOC REVIEW</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>Do not reply back to this e-mail!
+Hello,
+Thank you for submitting a document to the Chemical Safety Compliance Team.
+Upon review, we determined that the Safety Data Sheet ( SDS ) you uploaded for your ASIN is invalid due to it being incomplete, inaccurate, or otherwise conflicting, and thus, cannot be used for classification. Even though you've provided a written statement asserting that this SDS is the correct one, unfortunately, it doesn't validate its applicability for your product due to the following issues with the SDS:
+→ The name/title of the product on the SDS is " See item 3 for details " while the listing name/title of the product is "12 color acrylic paint ".
+→ The SDS must be composed in accordance with a valid regulation/legislation for Chemical Safety Compliance( for which your product is listed and stored ).
+The SDS does not include the legislation/regulation in accordance with the document was created
+Legislation/regulation should be also mentioned in section 2 “Hazard Identification”.
+→ The SDS must be composed in accordance with a valid regulation/legislation for Chemical Safety Compliance( for which your product is listed and stored ).
+The SDS does not include th</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 11 May 2026 09:19:28 +0000</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>"cscompliance-docreview-vendor@amazon.com.mx" &lt;cscompliance-docreview-vendor@amazon.com.mx&gt;</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 771770 - CSC
+ - DOC REVIEW</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>Do not reply back to this e-mail!
+Hello,
+Thank you for submitting a document to the Chemical Safety Compliance Team.
+Upon review, we determined that the Safety Data Sheet ( SDS ) you uploaded for your ASIN is invalid due to it being incomplete, inaccurate, or otherwise conflicting, and thus, cannot be used for classification. Even though you've provided a written statement asserting that this SDS is the correct one, unfortunately, it doesn't validate its applicability for your product due to the following issues with the SDS:
+→ The SDS must be composed in accordance with a valid regulation/legislation for Chemical Safety Compliance( for which your product is listed and stored ).
+The SDS does not include the legislation/regulation in accordance with the document was created
+Legislation/regulation should be also mentioned in section 2 “Hazard Identification”.
+For guidance on Safety Data Sheet requirements, please refer to https://sellercentral.amazon.com/help/hub/reference/G5G6BBSA6FZQP9CP
+Once you have corrected the problems listed above, please re-upload a valid document in Account Health Dashboard under "Regulatory Compliance" section. For any questions/appeals regarding these pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 11 May 2026 09:15:37 +0000</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0G6XCTGJC, MARKETPLACE:
+ A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>Do not reply back to this e-mail!
+Hello,
+Thank you for submitting a document to the Chemical Safety Compliance Team.
+Upon review, we determined that the Safety Data Sheet ( SDS ) you uploaded for your ASIN is invalid due to it being incomplete, inaccurate, or otherwise conflicting, and thus, cannot be used for classification. Even though you've provided a written statement asserting that this SDS is the correct one, unfortunately, it doesn't validate its applicability for your product due to the following issues with the SDS:
+→ The SDS must be composed in accordance with a valid regulation/legislation for Chemical Safety Compliance( for which your product is listed and stored ).
+The SDS does not include the legislation/regulation in accordance with the document was created
+Legislation/regulation should be also mentioned in section 2 “Hazard Identification”.
+For guidance on Safety Data Sheet requirements, please refer to https://sellercentral.amazon.com/help/hub/reference/G5G6BBSA6FZQP9CP
+Once you have corrected the problems listed above, please re-upload a valid document in Account Health Dashboard under "Regulatory Compliance" section. For any questions/appeals regarding these pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:37:14 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Votre facture pour les frais de paiement au titre de la REP pour
  les ventes sur Amazon.fr |   Your VAT invoice for EPR Pay on Behalf charges
  for Amazon.fr sales</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>Bonjour,
 Votre facture pour couvrant les frais de paiement au titre de la Responsabilité élargie du producteur (REP) pour les ventes sur Amazon.fr est désormais disponible.
@@ -3676,39 +3633,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 17:50:39 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -3727,39 +3684,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 12:49:24 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Submit missing VAT Registration Information</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -3783,39 +3740,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 02:13:07 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3833,39 +3790,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 13:18:47 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3883,39 +3840,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 13:15:01 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3933,39 +3890,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 02:13:49 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3983,39 +3940,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:19:29 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4033,39 +3990,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 12:52:07 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -4081,39 +4038,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:11:27 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4131,39 +4088,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 14:14:16 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4181,39 +4138,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 13:03:36 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility 96
  Complete Pan EU enrollment: Add NL products now
@@ -4223,39 +4180,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 09:05:17 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>【请勿回复此日志，如有问题请加入下方邮件中的企微群】
 卖家您好，
@@ -4276,39 +4233,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:13:11 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -4324,39 +4281,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:52:19 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -4375,39 +4332,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 03:13:33 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20093870001] Other account issues</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>Hello from Amazon Selling Partner Support,
 My name is Ritam. I am a Live Channel Specialist and I'm contacting you to follow up on your concern regarding the reinstatement of your listing B0FCDRNTT8.
@@ -4418,39 +4375,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Apr 2026 17:15:23 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -4469,39 +4426,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:15:37 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -4520,39 +4477,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:09:18 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -4571,39 +4528,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 03:03:00 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -4623,39 +4580,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 01:27:00 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20061337331] 对危险品分类提出异议</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家/供应商:您好!
 我们了解到您希望重新激活商品 ASIN: B0FCDRNTT8。
@@ -4684,39 +4641,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 10:07:05 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -4734,39 +4691,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:15:48 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4784,39 +4741,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:08:57 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4834,39 +4791,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 06:10:23 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>"compliance-ops-mass-programs@amazon.com" &lt;compliance-ops-mass-programs@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12449434352] 【邀请函】诚邀您参与亚马逊卖家合规策略调研</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>尊敬的销售伙伴，
 您好！
@@ -4880,39 +4837,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 21:09:24 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4930,40 +4887,40 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 14:16:35 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -4980,40 +4937,40 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 09:57:17 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -5030,39 +4987,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 16:06:35 +0800 (GMT+08:00)</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>苏浩然 &lt;suhr@cvc.org.cn&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Amazon DV TIC</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家，您好。
 我们可以为您提供亚马逊DV验证报告服务。
@@ -5096,39 +5053,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 10:14:18 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -5143,39 +5100,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 03:38:27 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are contacting you to let you know that you could be missing out on sales opportunities because of your incomplete listings.
@@ -5188,6 +5145,60 @@
  https://sellercentral.amazon.ca/performance/account/health/compliance-request
 If you need further help, please raise a case via contact us. - https://sellercentral.amazon.ca/cu/contact-us?ref=xx_ContactUs_xxxx_helphub
 If you are not the correct point of contact, please re-direct this email to the correct poin</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 11 May 2026 12:21:34 +0000</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>Dein Einkaufswagen wartet</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
+Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
+ -7 % 21,81 € UVP: 23,49 €
+https://www.amazon.de/gp/product/B0DRCB74YN/?ref_=
+Einkaufswagen anzeigen
+https://www.amazon.de/gp/cart/view.html?ref_=cor
+Schaue dir weitere Optionen an
+75x120 cm Feuerfeste Unterlage, Hitzeschutzmatte, Antihaft-Material Bodenschutzmatte, Grill Matten, Bodenmatte Feuerstellenmatte Outdoor BBQ Matte für Gasgrill Holzkohlegrill
+ 16,80 €
+https://www.amazon.de/gp/product/B0DBLM41YS/?ref_=ci_mcx_mr_2p_0_lm
+Alckijy Feuerfeste Unterlage | 100 * 150cm Faltbare Hitzeschutzmatte | Bodenschutzmatte | Grillmatten | Bodenmatte | Grillteppich | Funkenschutzplatte | für BBQ Grills Kaminöfen Boden Rasen usw
+ -4 % 20,15 € UVP: 20,97 €
+https://www.amazon.de/gp/product/B0CSGBZG8W/?ref_=ci_mcx_mr_2p_1_lm
+FLASLD Feuerfeste Matte Hitzebeständig Grillmatte unter Blackgrillstone, 40 x 60 cm schützt Ihren Vorbereitungstisch und Grilltisch im Freien – hitzebeständige Grilltischmatte schwarz
+ 8,39 €
+https://www.amazon.de/gp/product/B0C9ZR7PGP/?ref_=ci_mcx_mr_2p_2_lm
+We</t>
         </is>
       </c>
     </row>
@@ -9196,7 +9207,7 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>法务/侵权类</t>
+          <t>货件/库存类</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
@@ -9211,68 +9222,21 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>Sat, 18 Apr 2026 15:14:51 +0000</t>
+          <t>Sat, 9 May 2026 04:43:42 +0000</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>Pagamento elaborato con successo</t>
+          <t>Create FBA removal order by 2026-05-21</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr"/>
       <c r="H178" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
-This title will display on mobile devices
- Congratulazioni. Il pagamento è stato elaborato con successo e ti sarà accreditato a breve.
- Tentativo di pagamento
-Congratulazioni Weihai EU! Il pagamento è stato elaborato con successo e ti sarà accreditato nel giro di da tre a cinque giorni.
-In data 04/18/26 15:14 CEST, abbiamo avviato un trasferimento sul tuo metodo di pagamento (conto bancario che termina con 229) dell’importo di €
- 202,18.
- Se l’importo è inferiore a quanto atteso, tieni in considerazione le seguenti domande:
- Hai un saldo non disponibile? Amazon potrebbe trattenere una certa somma per coprire i costi di eventuali resi, reclami o contestazioni di una transazione (chargeback) da parte degli acquirenti. In questo caso, il saldo finale nel tuo report sui pagamenti mostrerà il saldo non disponibile corrispondente alla cifra trattenuta.
- Le tue vendite coprono tutte le commissioni e i resi per questo ciclo di fatturazione? L’importo del pagamento rispecchia le attività di vendita, le commissioni di vendita e le tariffe per promozioni o servizi. Ti consigliamo di rivedere il report sui pagamenti nella scheda Report di Seller Central per comprendere le diverse spese che </t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B179" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C179" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D179" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 9 May 2026 04:43:42 +0000</t>
-        </is>
-      </c>
-      <c r="E179" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F179" s="2" t="inlineStr">
-        <is>
-          <t>Create FBA removal order by 2026-05-21</t>
-        </is>
-      </c>
-      <c r="G179" s="2" t="inlineStr"/>
-      <c r="H179" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -9296,39 +9260,39 @@
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="2" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B180" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C180" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D180" s="2" t="inlineStr">
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 03:34:49 +0000</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="E179" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F180" s="2" t="inlineStr">
+      <c r="F179" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr"/>
-      <c r="H180" s="2" t="inlineStr">
+      <c r="G179" s="2" t="inlineStr"/>
+      <c r="H179" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -9351,39 +9315,39 @@
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="2" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B181" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C181" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D181" s="2" t="inlineStr">
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 04:46:00 +0000</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="E180" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F181" s="2" t="inlineStr">
+      <c r="F180" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G181" s="2" t="inlineStr"/>
-      <c r="H181" s="2" t="inlineStr">
+      <c r="G180" s="2" t="inlineStr"/>
+      <c r="H180" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -9407,39 +9371,39 @@
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="2" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B182" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C182" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D182" s="2" t="inlineStr">
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 04:25:43 +0000</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr">
+      <c r="E181" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F182" s="2" t="inlineStr">
+      <c r="F181" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G182" s="2" t="inlineStr"/>
-      <c r="H182" s="2" t="inlineStr">
+      <c r="G181" s="2" t="inlineStr"/>
+      <c r="H181" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -9463,39 +9427,39 @@
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="2" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B183" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C183" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D183" s="2" t="inlineStr">
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 03:35:07 +0000</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="E182" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F183" s="2" t="inlineStr">
+      <c r="F182" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-07</t>
         </is>
       </c>
-      <c r="G183" s="2" t="inlineStr"/>
-      <c r="H183" s="2" t="inlineStr">
+      <c r="G182" s="2" t="inlineStr"/>
+      <c r="H182" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -9516,10 +9480,51 @@
         </is>
       </c>
     </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>其他风险类</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 11 May 2026 11:38:29 +0000</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>You have until July 11 to verify FBA dimensions for fee calculation</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr"/>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">As previously communicated, we've updated the way we collect Fulfilment by Amazon (FBA) item package dimensions for products listed in our UK, Germany, France, Italy and Spain stores.
+ 96
+ As previously communicated, we've updated the way we collect Fulfilment by Amazon (FBA) item package dimensions for products listed in our UK, Germany, France, Italy and Spain stores.
+                                                     ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ </t>
+        </is>
+      </c>
+    </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>货件/库存类</t>
+          <t>其他风险类</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
@@ -9534,130 +9539,21 @@
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>Sat, 18 Apr 2026 04:00:50 +0000</t>
+          <t>Fri, 1 May 2026 00:16:37 +0000</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
+          <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>Create FBA removal order by 2026-04-30</t>
+          <t>View your US Q2-2026 CSBA fee rate</t>
         </is>
       </c>
       <c r="G184" s="2" t="inlineStr"/>
       <c r="H184" s="2" t="inlineStr">
-        <is>
-          <t>96
-Automated removals of unfulfillable inventory
- Required removals: First notification
- Required removals: First notification
- Hello,
-Your FBA inventory listed below became unsellable in the past seven days. You must create a removal order by 2026-04-30 or these items will be disposed of. Removal fees will apply. Review the affected items and next steps below.
-Unsellable products:
-- FNSKU: X0025OEJ4F Quantity: 1
-- FNSKU: X002A05YW5 Quantity: 2
- Why is this happening?
-This action is required because these items are no longer in sellable condition in our fulfilment centres. According to our FBA Required Removals policy, all unsuitable units must be removed within 14 days of notification. To learn more, go to our FBA Required Removals policy .
-We leveraged a combination of automated means to identify this issue and make this decision.
- How do I address this?
-Follow these steps to manage your unsellable inventory:
-- Check your complete list and quantity of unsellable items in the Manage FBA inventory .
-- Create a removal order (removal fees apply) by following the instructions in Remove inventory overview .
- To avoid future manual inventory removal orders, set up Automated Unfulfillab</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B185" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C185" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D185" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 18 Apr 2026 03:30:46 +0000</t>
-        </is>
-      </c>
-      <c r="E185" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F185" s="2" t="inlineStr">
-        <is>
-          <t>Disposal order created for unsellable FBA inventory</t>
-        </is>
-      </c>
-      <c r="G185" s="2" t="inlineStr"/>
-      <c r="H185" s="2" t="inlineStr">
-        <is>
-          <t>96
-Automated Removals of Unfulfillable Inventory
- Final notice: Disposal order for your unfulfillable FBA inventory
- Final notice: Disposal order for your unfulfillable FBA inventory
- Hello,
-You have unfulfillable inventory that has been in a fulfilment centre for more than 14 days. We have created a disposal order for these items.
- Why is this happening?
-This action is required because these unfulfillable items have remained in our fulfilment centres for more than 14 days after notification. According to our FBA Required Removals policy, cancelling a required removal order is not permitted. To learn more, visit our FBA Required Removals policy .
- Removal order ID:
-- 8O0kSGupQP
- Unsellable Products:
-- FNSKU: X002A05YW5 Quantity: 1
- For more information about the disposal order process, see Remove inventory from a fulfilment centre .
- To monitor your unfulfillable inventory, see the Manage FBA Inventory for total unsellable quantities or the Recommended Removal report for unsellable and aged inventory details.
- The Fulfilment by Amazon Team
- Report an issue with this email
- If you have any questions visit: Seller Central
- To change your email preferences visit: Notification Preferen</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B186" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C186" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D186" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 1 May 2026 00:16:37 +0000</t>
-        </is>
-      </c>
-      <c r="E186" s="2" t="inlineStr">
-        <is>
-          <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F186" s="2" t="inlineStr">
-        <is>
-          <t>View your US Q2-2026 CSBA fee rate</t>
-        </is>
-      </c>
-      <c r="G186" s="2" t="inlineStr"/>
-      <c r="H186" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q2-2026
@@ -9687,39 +9583,39 @@
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="2" t="inlineStr">
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B187" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C187" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D187" s="2" t="inlineStr">
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 18:05:15 +0000</t>
         </is>
       </c>
-      <c r="E187" s="2" t="inlineStr">
+      <c r="E185" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F187" s="2" t="inlineStr">
+      <c r="F185" s="2" t="inlineStr">
         <is>
           <t>提交商品合规文件，以避免商品被移除</t>
         </is>
       </c>
-      <c r="G187" s="2" t="inlineStr"/>
-      <c r="H187" s="2" t="inlineStr">
+      <c r="G185" s="2" t="inlineStr"/>
+      <c r="H185" s="2" t="inlineStr">
         <is>
           <t>96
  提交商品合规文件，以避免商品被移除
@@ -9768,47 +9664,6 @@
         </is>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B188" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C188" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D188" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 18 Apr 2026 11:41:39 +0800 (GMT+08:00)</t>
-        </is>
-      </c>
-      <c r="E188" s="2" t="inlineStr">
-        <is>
-          <t>GTTC国际业务部玩具组 &lt;gttctoy@cngttc.cn&gt;</t>
-        </is>
-      </c>
-      <c r="F188" s="2" t="inlineStr">
-        <is>
-          <t>AMAZON DV TIC TRF ID--Top urgently</t>
-        </is>
-      </c>
-      <c r="G188" s="2" t="inlineStr"/>
-      <c r="H188" s="2" t="inlineStr">
-        <is>
-          <t>Dear Vendor,        Some of your TR numbers on Amazon have been pending in our backend for a long time without timely processing. We plan to automatically clear all unresponded TR numbers in our system two days later.
-If you have any TR numbers that require sample submission for testing, please reply to this email and send us the corresponding TR numbers within two days, and contact our relevant customer service within one week to arrange sample submission.
- For orders tested at third-party cooperative institutions, please promptly contact the person in charge of your institution and ask them to send the relevant TR numbers to us as soon as possible for registration and processing.   If need, pls Contact us @ below : 1.Mr.Zhang (张豪林） Mobile: +86 17363401067 Wechat code:
-2. Lisa Li (李桂珍) Mobile: +86 13760771124 phone No: 020-6634 8679 Email: lisalee@gttc.net.cn Best Regards, Apollo Luo罗武波 Mobile: +86 13580360968 Phone: 020-6634 8593 Email: apolloluo@gttc.net.cn</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
